--- a/artfynd/A 10323-2026 artfynd.xlsx
+++ b/artfynd/A 10323-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131540723</v>
       </c>
       <c r="B2" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131539444</v>
       </c>
       <c r="B3" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131539470</v>
       </c>
       <c r="B4" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131540768</v>
       </c>
       <c r="B5" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>131540065</v>
       </c>
       <c r="B6" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>131539778</v>
       </c>
       <c r="B7" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>131539310</v>
       </c>
       <c r="B8" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>131539430</v>
       </c>
       <c r="B9" t="n">
-        <v>92281</v>
+        <v>92287</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>131540813</v>
       </c>
       <c r="B10" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>131539572</v>
       </c>
       <c r="B11" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>131539894</v>
       </c>
       <c r="B12" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>131539396</v>
       </c>
       <c r="B13" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>131540707</v>
       </c>
       <c r="B14" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>131540671</v>
       </c>
       <c r="B15" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 10323-2026 artfynd.xlsx
+++ b/artfynd/A 10323-2026 artfynd.xlsx
@@ -1728,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131539894</v>
+        <v>131539396</v>
       </c>
       <c r="B12" t="n">
-        <v>91828</v>
+        <v>92126</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1739,24 +1739,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1766,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509272</v>
+        <v>508849</v>
       </c>
       <c r="R12" t="n">
-        <v>6713529</v>
+        <v>6713459</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1829,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131539396</v>
+        <v>131539894</v>
       </c>
       <c r="B13" t="n">
-        <v>92126</v>
+        <v>91828</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1840,28 +1844,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508849</v>
+        <v>509272</v>
       </c>
       <c r="R13" t="n">
-        <v>6713459</v>
+        <v>6713529</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 10323-2026 artfynd.xlsx
+++ b/artfynd/A 10323-2026 artfynd.xlsx
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131539430</v>
+        <v>131540813</v>
       </c>
       <c r="B9" t="n">
-        <v>92287</v>
+        <v>99033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,26 +1427,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1454,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508843</v>
+        <v>509269</v>
       </c>
       <c r="R9" t="n">
-        <v>6713455</v>
+        <v>6713493</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1517,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131540813</v>
+        <v>131539430</v>
       </c>
       <c r="B10" t="n">
-        <v>99033</v>
+        <v>92287</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1528,35 +1537,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509269</v>
+        <v>508843</v>
       </c>
       <c r="R10" t="n">
-        <v>6713493</v>
+        <v>6713455</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 10323-2026 artfynd.xlsx
+++ b/artfynd/A 10323-2026 artfynd.xlsx
@@ -981,7 +981,7 @@
         <v>131540768</v>
       </c>
       <c r="B5" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>131540065</v>
       </c>
       <c r="B6" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>131539778</v>
       </c>
       <c r="B7" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131540813</v>
+        <v>131539430</v>
       </c>
       <c r="B9" t="n">
-        <v>99033</v>
+        <v>92288</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,35 +1427,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1463,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509269</v>
+        <v>508843</v>
       </c>
       <c r="R9" t="n">
-        <v>6713493</v>
+        <v>6713455</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1526,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131539430</v>
+        <v>131540813</v>
       </c>
       <c r="B10" t="n">
-        <v>92287</v>
+        <v>99034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1537,26 +1528,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508843</v>
+        <v>509269</v>
       </c>
       <c r="R10" t="n">
-        <v>6713455</v>
+        <v>6713493</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1630,7 +1630,7 @@
         <v>131539572</v>
       </c>
       <c r="B11" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131539396</v>
+        <v>131539894</v>
       </c>
       <c r="B12" t="n">
-        <v>92126</v>
+        <v>91828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1739,28 +1739,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1770,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508849</v>
+        <v>509272</v>
       </c>
       <c r="R12" t="n">
-        <v>6713459</v>
+        <v>6713529</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1833,10 +1829,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131539894</v>
+        <v>131539396</v>
       </c>
       <c r="B13" t="n">
-        <v>91828</v>
+        <v>92127</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,24 +1840,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509272</v>
+        <v>508849</v>
       </c>
       <c r="R13" t="n">
-        <v>6713529</v>
+        <v>6713459</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1937,7 +1937,7 @@
         <v>131540707</v>
       </c>
       <c r="B14" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 10323-2026 artfynd.xlsx
+++ b/artfynd/A 10323-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131540723</v>
       </c>
       <c r="B2" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131539444</v>
       </c>
       <c r="B3" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131539470</v>
       </c>
       <c r="B4" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131540768</v>
       </c>
       <c r="B5" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>131540065</v>
       </c>
       <c r="B6" t="n">
-        <v>92127</v>
+        <v>92128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>131539778</v>
       </c>
       <c r="B7" t="n">
-        <v>92127</v>
+        <v>92128</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>131539310</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>131539430</v>
       </c>
       <c r="B9" t="n">
-        <v>92288</v>
+        <v>92289</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>131540813</v>
       </c>
       <c r="B10" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>131539572</v>
       </c>
       <c r="B11" t="n">
-        <v>92127</v>
+        <v>92128</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>131539894</v>
       </c>
       <c r="B12" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>131539396</v>
       </c>
       <c r="B13" t="n">
-        <v>92127</v>
+        <v>92128</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>131540707</v>
       </c>
       <c r="B14" t="n">
-        <v>92127</v>
+        <v>92128</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>131540671</v>
       </c>
       <c r="B15" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 10323-2026 artfynd.xlsx
+++ b/artfynd/A 10323-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131540723</v>
       </c>
       <c r="B2" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131539444</v>
       </c>
       <c r="B3" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131539470</v>
       </c>
       <c r="B4" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131540768</v>
       </c>
       <c r="B5" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>131540065</v>
       </c>
       <c r="B6" t="n">
-        <v>92128</v>
+        <v>92131</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>131539778</v>
       </c>
       <c r="B7" t="n">
-        <v>92128</v>
+        <v>92131</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>131539310</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>131539430</v>
       </c>
       <c r="B9" t="n">
-        <v>92289</v>
+        <v>92292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>131540813</v>
       </c>
       <c r="B10" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>131539572</v>
       </c>
       <c r="B11" t="n">
-        <v>92128</v>
+        <v>92131</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>131539894</v>
       </c>
       <c r="B12" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>131539396</v>
       </c>
       <c r="B13" t="n">
-        <v>92128</v>
+        <v>92131</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>131540707</v>
       </c>
       <c r="B14" t="n">
-        <v>92128</v>
+        <v>92131</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>131540671</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 10323-2026 artfynd.xlsx
+++ b/artfynd/A 10323-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131540723</v>
       </c>
       <c r="B2" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131539444</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131539470</v>
       </c>
       <c r="B4" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131540768</v>
       </c>
       <c r="B5" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>131540065</v>
       </c>
       <c r="B6" t="n">
-        <v>92131</v>
+        <v>92137</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>131539778</v>
       </c>
       <c r="B7" t="n">
-        <v>92131</v>
+        <v>92137</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>131539310</v>
       </c>
       <c r="B8" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131539430</v>
+        <v>131540813</v>
       </c>
       <c r="B9" t="n">
-        <v>92292</v>
+        <v>99044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,26 +1427,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1454,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508843</v>
+        <v>509269</v>
       </c>
       <c r="R9" t="n">
-        <v>6713455</v>
+        <v>6713493</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1517,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131540813</v>
+        <v>131539430</v>
       </c>
       <c r="B10" t="n">
-        <v>99038</v>
+        <v>92298</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1528,35 +1537,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509269</v>
+        <v>508843</v>
       </c>
       <c r="R10" t="n">
-        <v>6713493</v>
+        <v>6713455</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1630,7 +1630,7 @@
         <v>131539572</v>
       </c>
       <c r="B11" t="n">
-        <v>92131</v>
+        <v>92137</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>131539894</v>
       </c>
       <c r="B12" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>131539396</v>
       </c>
       <c r="B13" t="n">
-        <v>92131</v>
+        <v>92137</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>131540707</v>
       </c>
       <c r="B14" t="n">
-        <v>92131</v>
+        <v>92137</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>131540671</v>
       </c>
       <c r="B15" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 10323-2026 artfynd.xlsx
+++ b/artfynd/A 10323-2026 artfynd.xlsx
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131540813</v>
+        <v>131539430</v>
       </c>
       <c r="B9" t="n">
-        <v>99044</v>
+        <v>92298</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,35 +1427,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1463,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509269</v>
+        <v>508843</v>
       </c>
       <c r="R9" t="n">
-        <v>6713493</v>
+        <v>6713455</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1526,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131539430</v>
+        <v>131540813</v>
       </c>
       <c r="B10" t="n">
-        <v>92298</v>
+        <v>99044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1537,26 +1528,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508843</v>
+        <v>509269</v>
       </c>
       <c r="R10" t="n">
-        <v>6713455</v>
+        <v>6713493</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 10323-2026 artfynd.xlsx
+++ b/artfynd/A 10323-2026 artfynd.xlsx
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131539430</v>
+        <v>131540813</v>
       </c>
       <c r="B9" t="n">
-        <v>92298</v>
+        <v>99044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,26 +1427,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1454,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508843</v>
+        <v>509269</v>
       </c>
       <c r="R9" t="n">
-        <v>6713455</v>
+        <v>6713493</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1517,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131540813</v>
+        <v>131539430</v>
       </c>
       <c r="B10" t="n">
-        <v>99044</v>
+        <v>92298</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1528,35 +1537,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509269</v>
+        <v>508843</v>
       </c>
       <c r="R10" t="n">
-        <v>6713493</v>
+        <v>6713455</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 10323-2026 artfynd.xlsx
+++ b/artfynd/A 10323-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131540723</v>
+        <v>131539444</v>
       </c>
       <c r="B2" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509275</v>
+        <v>508848</v>
       </c>
       <c r="R2" t="n">
-        <v>6713503</v>
+        <v>6713454</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131539444</v>
+        <v>131540723</v>
       </c>
       <c r="B3" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508848</v>
+        <v>509275</v>
       </c>
       <c r="R3" t="n">
-        <v>6713454</v>
+        <v>6713503</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,7 +880,7 @@
         <v>131539470</v>
       </c>
       <c r="B4" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131540768</v>
       </c>
       <c r="B5" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>131540065</v>
       </c>
       <c r="B6" t="n">
-        <v>92137</v>
+        <v>92140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>131539778</v>
       </c>
       <c r="B7" t="n">
-        <v>92137</v>
+        <v>92140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>131539310</v>
       </c>
       <c r="B8" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131539430</v>
+        <v>131540813</v>
       </c>
       <c r="B9" t="n">
-        <v>92298</v>
+        <v>99047</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,26 +1427,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1454,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508843</v>
+        <v>509269</v>
       </c>
       <c r="R9" t="n">
-        <v>6713455</v>
+        <v>6713493</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1517,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131540813</v>
+        <v>131539430</v>
       </c>
       <c r="B10" t="n">
-        <v>99044</v>
+        <v>92301</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1528,35 +1537,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509269</v>
+        <v>508843</v>
       </c>
       <c r="R10" t="n">
-        <v>6713493</v>
+        <v>6713455</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1630,7 +1630,7 @@
         <v>131539572</v>
       </c>
       <c r="B11" t="n">
-        <v>92137</v>
+        <v>92140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>131539894</v>
       </c>
       <c r="B12" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>131539396</v>
       </c>
       <c r="B13" t="n">
-        <v>92137</v>
+        <v>92140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>131540707</v>
       </c>
       <c r="B14" t="n">
-        <v>92137</v>
+        <v>92140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>131540671</v>
       </c>
       <c r="B15" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 10323-2026 artfynd.xlsx
+++ b/artfynd/A 10323-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131539444</v>
+        <v>131540723</v>
       </c>
       <c r="B2" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508848</v>
+        <v>509275</v>
       </c>
       <c r="R2" t="n">
-        <v>6713454</v>
+        <v>6713503</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131540723</v>
+        <v>131539444</v>
       </c>
       <c r="B3" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509275</v>
+        <v>508848</v>
       </c>
       <c r="R3" t="n">
-        <v>6713503</v>
+        <v>6713454</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,7 +880,7 @@
         <v>131539470</v>
       </c>
       <c r="B4" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131540768</v>
       </c>
       <c r="B5" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>131540065</v>
       </c>
       <c r="B6" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>131539778</v>
       </c>
       <c r="B7" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>131539310</v>
       </c>
       <c r="B8" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131540813</v>
+        <v>131539430</v>
       </c>
       <c r="B9" t="n">
-        <v>99047</v>
+        <v>92306</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,35 +1427,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1463,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509269</v>
+        <v>508843</v>
       </c>
       <c r="R9" t="n">
-        <v>6713493</v>
+        <v>6713455</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1526,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131539430</v>
+        <v>131540813</v>
       </c>
       <c r="B10" t="n">
-        <v>92301</v>
+        <v>99052</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1537,26 +1528,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508843</v>
+        <v>509269</v>
       </c>
       <c r="R10" t="n">
-        <v>6713455</v>
+        <v>6713493</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1630,7 +1630,7 @@
         <v>131539572</v>
       </c>
       <c r="B11" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>131539894</v>
       </c>
       <c r="B12" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>131539396</v>
       </c>
       <c r="B13" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>131540707</v>
       </c>
       <c r="B14" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>131540671</v>
       </c>
       <c r="B15" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 10323-2026 artfynd.xlsx
+++ b/artfynd/A 10323-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131540723</v>
       </c>
       <c r="B2" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131539444</v>
       </c>
       <c r="B3" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131539470</v>
       </c>
       <c r="B4" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131540768</v>
       </c>
       <c r="B5" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>131540065</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92147</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>131539778</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92147</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>131539310</v>
       </c>
       <c r="B8" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131539430</v>
+        <v>131540813</v>
       </c>
       <c r="B9" t="n">
-        <v>92306</v>
+        <v>99054</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,26 +1427,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1454,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508843</v>
+        <v>509269</v>
       </c>
       <c r="R9" t="n">
-        <v>6713455</v>
+        <v>6713493</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1517,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131540813</v>
+        <v>131539430</v>
       </c>
       <c r="B10" t="n">
-        <v>99052</v>
+        <v>92308</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1528,35 +1537,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509269</v>
+        <v>508843</v>
       </c>
       <c r="R10" t="n">
-        <v>6713493</v>
+        <v>6713455</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1630,7 +1630,7 @@
         <v>131539572</v>
       </c>
       <c r="B11" t="n">
-        <v>92145</v>
+        <v>92147</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>131539894</v>
       </c>
       <c r="B12" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>131539396</v>
       </c>
       <c r="B13" t="n">
-        <v>92145</v>
+        <v>92147</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>131540707</v>
       </c>
       <c r="B14" t="n">
-        <v>92145</v>
+        <v>92147</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>131540671</v>
       </c>
       <c r="B15" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 10323-2026 artfynd.xlsx
+++ b/artfynd/A 10323-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131540723</v>
+        <v>131539337</v>
       </c>
       <c r="B2" t="n">
-        <v>91848</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,24 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -713,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509275</v>
+        <v>508817</v>
       </c>
       <c r="R2" t="n">
-        <v>6713503</v>
+        <v>6713460</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131539444</v>
+        <v>131539396</v>
       </c>
       <c r="B3" t="n">
-        <v>91848</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,24 +791,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -814,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508848</v>
+        <v>508849</v>
       </c>
       <c r="R3" t="n">
-        <v>6713454</v>
+        <v>6713459</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131539470</v>
+        <v>131539444</v>
       </c>
       <c r="B4" t="n">
-        <v>91848</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509026</v>
+        <v>508848</v>
       </c>
       <c r="R4" t="n">
-        <v>6713453</v>
+        <v>6713454</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,46 +986,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131540768</v>
+        <v>131539430</v>
       </c>
       <c r="B5" t="n">
-        <v>99054</v>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1025,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509276</v>
+        <v>508843</v>
       </c>
       <c r="R5" t="n">
-        <v>6713493</v>
+        <v>6713455</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131540065</v>
+        <v>131539572</v>
       </c>
       <c r="B6" t="n">
-        <v>92147</v>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,11 +1115,7 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1130,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509278</v>
+        <v>509227</v>
       </c>
       <c r="R6" t="n">
-        <v>6713526</v>
+        <v>6713542</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,7 +1191,7 @@
         <v>131539778</v>
       </c>
       <c r="B7" t="n">
-        <v>92147</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131539310</v>
+        <v>131540065</v>
       </c>
       <c r="B8" t="n">
-        <v>57914</v>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1309,39 +1304,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1349,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508964</v>
+        <v>509278</v>
       </c>
       <c r="R8" t="n">
-        <v>6713446</v>
+        <v>6713526</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1387,17 +1373,13 @@
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosöker i levande men av insekter angripen äldre gran.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1416,46 +1398,41 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131540813</v>
+        <v>131540707</v>
       </c>
       <c r="B9" t="n">
-        <v>99054</v>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1463,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509269</v>
+        <v>509271</v>
       </c>
       <c r="R9" t="n">
-        <v>6713493</v>
+        <v>6713501</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1526,32 +1503,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131539430</v>
+        <v>131539470</v>
       </c>
       <c r="B10" t="n">
-        <v>92308</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1564,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508843</v>
+        <v>509026</v>
       </c>
       <c r="R10" t="n">
-        <v>6713455</v>
+        <v>6713453</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1627,10 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131539572</v>
+        <v>131539894</v>
       </c>
       <c r="B11" t="n">
-        <v>92147</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1638,21 +1615,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1665,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509227</v>
+        <v>509272</v>
       </c>
       <c r="R11" t="n">
-        <v>6713542</v>
+        <v>6713529</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1728,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131539894</v>
+        <v>131540723</v>
       </c>
       <c r="B12" t="n">
-        <v>91848</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509272</v>
+        <v>509275</v>
       </c>
       <c r="R12" t="n">
-        <v>6713529</v>
+        <v>6713503</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1829,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131539396</v>
+        <v>131540837</v>
       </c>
       <c r="B13" t="n">
-        <v>92147</v>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1840,28 +1817,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1871,10 +1844,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508849</v>
+        <v>509278</v>
       </c>
       <c r="R13" t="n">
-        <v>6713459</v>
+        <v>6713485</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1934,10 +1907,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131540707</v>
+        <v>131539310</v>
       </c>
       <c r="B14" t="n">
-        <v>92147</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,30 +1918,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1976,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509271</v>
+        <v>508964</v>
       </c>
       <c r="R14" t="n">
-        <v>6713501</v>
+        <v>6713446</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2014,13 +1996,17 @@
           <t>2026-03-09</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosöker i levande men av insekter angripen äldre gran.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2042,7 +2028,7 @@
         <v>131540671</v>
       </c>
       <c r="B15" t="n">
-        <v>57914</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,6 +2132,336 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131540768</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Djurmo klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>509276</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6713493</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131540813</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Djurmo klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>509269</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6713493</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131540827</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Djurmo klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>509275</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6713475</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
